--- a/artfynd/A 57776-2025 artfynd.xlsx
+++ b/artfynd/A 57776-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127660672</v>
+        <v>127660654</v>
       </c>
       <c r="B2" t="n">
-        <v>98499</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701102</v>
+        <v>701073</v>
       </c>
       <c r="R2" t="n">
-        <v>7097649</v>
+        <v>7097598</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127660688</v>
+        <v>127660643</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701096</v>
+        <v>701085</v>
       </c>
       <c r="R3" t="n">
-        <v>7097712</v>
+        <v>7097565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127660653</v>
+        <v>127660644</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701087</v>
+        <v>701124</v>
       </c>
       <c r="R4" t="n">
-        <v>7097573</v>
+        <v>7097547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,37 +1005,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127660689</v>
+        <v>127660645</v>
       </c>
       <c r="B5" t="n">
-        <v>98499</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701123</v>
+        <v>701137</v>
       </c>
       <c r="R5" t="n">
-        <v>7097706</v>
+        <v>7097537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,37 +1115,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127660654</v>
+        <v>127660649</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701073</v>
+        <v>701103</v>
       </c>
       <c r="R6" t="n">
-        <v>7097598</v>
+        <v>7097574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,37 +1225,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127660687</v>
+        <v>127660653</v>
       </c>
       <c r="B7" t="n">
-        <v>98499</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701116</v>
+        <v>701087</v>
       </c>
       <c r="R7" t="n">
-        <v>7097694</v>
+        <v>7097573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127660643</v>
+        <v>127660655</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701085</v>
+        <v>701130</v>
       </c>
       <c r="R8" t="n">
-        <v>7097565</v>
+        <v>7097578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127660649</v>
+        <v>127660660</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701103</v>
+        <v>701115</v>
       </c>
       <c r="R9" t="n">
-        <v>7097574</v>
+        <v>7097607</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,37 +1555,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127660651</v>
+        <v>127660661</v>
       </c>
       <c r="B10" t="n">
-        <v>98499</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701091</v>
+        <v>701130</v>
       </c>
       <c r="R10" t="n">
-        <v>7097569</v>
+        <v>7097599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,6 +1658,1216 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127660674</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>701141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7097628</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127660685</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701141</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7097667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127660686</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701134</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7097680</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127660688</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701096</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7097712</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127660691</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>701137</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7097689</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127660692</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>701151</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7097673</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127660651</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701091</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7097569</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127660672</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>701102</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7097649</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127660673</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>701123</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7097639</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127660687</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>701116</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7097694</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127660689</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Degernäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>701123</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7097706</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
